--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1459654980</v>
+        <v>1456540785</v>
       </c>
       <c r="E2" t="n">
-        <v>386967946.83</v>
+        <v>386856021.9525</v>
       </c>
       <c r="F2" t="n">
-        <v>1072687033.17</v>
+        <v>1069684763.0475</v>
       </c>
       <c r="G2" t="n">
-        <v>2.796715078334091</v>
+        <v>2.804564581674595</v>
       </c>
       <c r="H2" t="n">
         <v>8590000000</v>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1456540785</v>
+        <v>1460066748</v>
       </c>
       <c r="E2" t="n">
-        <v>386856021.9525</v>
+        <v>381924081.7575</v>
       </c>
       <c r="F2" t="n">
-        <v>1069684763.0475</v>
+        <v>1078142666.2425</v>
       </c>
       <c r="G2" t="n">
-        <v>2.804564581674595</v>
+        <v>2.782563100350606</v>
       </c>
       <c r="H2" t="n">
         <v>8590000000</v>

--- a/liq_calc/output/lcr_nsfr_report.xlsx
+++ b/liq_calc/output/lcr_nsfr_report.xlsx
@@ -485,16 +485,16 @@
         <v>3000000000</v>
       </c>
       <c r="D2" t="n">
-        <v>1460066748</v>
+        <v>1401576939</v>
       </c>
       <c r="E2" t="n">
-        <v>381924081.7575</v>
+        <v>372601941.345</v>
       </c>
       <c r="F2" t="n">
-        <v>1078142666.2425</v>
+        <v>1028974997.655</v>
       </c>
       <c r="G2" t="n">
-        <v>2.782563100350606</v>
+        <v>2.915522735573654</v>
       </c>
       <c r="H2" t="n">
         <v>8590000000</v>
